--- a/experiment/Omni_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/Omni_bestx4/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.04</v>
+        <v>24.05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5715</v>
+        <v>0.5741000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.74</v>
+        <v>28.78</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8133</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.49</v>
+        <v>26.54</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8116</v>
+        <v>0.8131</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.63</v>
+        <v>30.66</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8485</v>
+        <v>0.8496</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.26</v>
+        <v>26.28</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7103</v>
+        <v>0.7131999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.87</v>
+        <v>34.01</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8929</v>
+        <v>0.8938</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.29</v>
+        <v>26.28</v>
       </c>
       <c r="C8" t="n">
-        <v>0.751</v>
+        <v>0.7507</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>23.09</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5915</v>
+        <v>0.5939</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.43</v>
+        <v>27.45</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7866</v>
+        <v>0.7879</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.33</v>
+        <v>29.36</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8033</v>
+        <v>0.8046</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.58</v>
+        <v>24.77</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7343</v>
+        <v>0.7442</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.98</v>
+        <v>28.07</v>
       </c>
       <c r="C13" t="n">
-        <v>0.751</v>
+        <v>0.7566000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.02</v>
+        <v>30.03</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8078</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.38</v>
+        <v>29.46</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8313</v>
+        <v>0.8345</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.03</v>
+        <v>25.02</v>
       </c>
       <c r="C16" t="n">
-        <v>0.678</v>
+        <v>0.6794</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.81</v>
+        <v>24.72</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7583</v>
+        <v>0.7597</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +663,7 @@
         <v>34.75</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8931</v>
+        <v>0.8935999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8939</v>
+        <v>0.8961</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.16</v>
+        <v>26.19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7375</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.02</v>
+        <v>26.05</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7996</v>
+        <v>0.8022</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.2</v>
+        <v>22.21</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6895</v>
+        <v>0.6944</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.81</v>
+        <v>23.91</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6251</v>
+        <v>0.6324</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24.84</v>
+        <v>24.83</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5724</v>
+        <v>0.5736</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.6</v>
+        <v>26.66</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7933</v>
+        <v>0.7969000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>27.69</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8224</v>
+        <v>0.8235</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26.98</v>
+        <v>26.95</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8383</v>
+        <v>0.8387</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.73</v>
+        <v>27.76</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7366</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.55</v>
+        <v>29.56</v>
       </c>
       <c r="C29" t="n">
-        <v>0.801</v>
+        <v>0.8018999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.46</v>
+        <v>32.64</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8992</v>
+        <v>0.9012</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.91</v>
+        <v>19.9</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5053</v>
+        <v>0.5086000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.78</v>
+        <v>29.8</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8183</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         <v>20.92</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4279</v>
+        <v>0.4321</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.19</v>
+        <v>25.18</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6712</v>
+        <v>0.6736</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.52</v>
+        <v>24.5</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7599</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.96</v>
+        <v>34.91</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8933</v>
+        <v>0.8934</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         <v>27.03</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7427</v>
+        <v>0.7453</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.93</v>
+        <v>27.94</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5133</v>
+        <v>0.5142</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.24</v>
+        <v>28.29</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7166</v>
+        <v>0.7187</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.49</v>
+        <v>28.5</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7454</v>
+        <v>0.7462</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.03</v>
+        <v>36.26</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9569</v>
+        <v>0.9584</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.85</v>
+        <v>26.83</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7447</v>
+        <v>0.7463</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.86</v>
+        <v>25.9</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7224</v>
+        <v>0.7252</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.78</v>
+        <v>26.79</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7603</v>
+        <v>0.7621</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27.95</v>
+        <v>28.06</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8744</v>
+        <v>0.8769</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.79</v>
+        <v>24.82</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6795</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.66</v>
+        <v>34.71</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8708</v>
+        <v>0.8718</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.81</v>
+        <v>22.79</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6242</v>
+        <v>0.6266</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24.97</v>
+        <v>25</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6339</v>
+        <v>0.6374</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.12</v>
+        <v>27.35</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8732</v>
+        <v>0.8784</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.18</v>
+        <v>32.19</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8398</v>
+        <v>0.8407</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.82</v>
+        <v>24.84</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6183</v>
+        <v>0.6213</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.45</v>
+        <v>22.62</v>
       </c>
       <c r="C53" t="n">
-        <v>0.703</v>
+        <v>0.7092000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.5</v>
+        <v>32.59</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8451</v>
+        <v>0.8472</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.57</v>
+        <v>32.58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8004</v>
+        <v>0.8008999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.74</v>
+        <v>27.78</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7762</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.6</v>
+        <v>25.63</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6933</v>
+        <v>0.6957</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21.45</v>
+        <v>21.46</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4234</v>
+        <v>0.4277</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.5</v>
+        <v>27.53</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7281</v>
+        <v>0.7304</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32.01</v>
+        <v>32.02</v>
       </c>
       <c r="C60" t="n">
-        <v>0.792</v>
+        <v>0.7927999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.23</v>
+        <v>31.3</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7849</v>
+        <v>0.7866</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8155</v>
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28.98</v>
+        <v>28.96</v>
       </c>
       <c r="C63" t="n">
-        <v>0.793</v>
+        <v>0.7932</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33.79</v>
+        <v>33.91</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9524</v>
+        <v>0.9532</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.32</v>
+        <v>24.34</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6724</v>
+        <v>0.6748</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26.06</v>
+        <v>26.04</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6212</v>
+        <v>0.6226</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.32</v>
+        <v>28.37</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7932</v>
+        <v>0.7951</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>40</v>
+        <v>40.14</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9807</v>
+        <v>0.9812</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.04</v>
+        <v>20.98</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.79</v>
+        <v>22.81</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6503</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>28.89</v>
+        <v>28.98</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8106</v>
+        <v>0.8131</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.49</v>
+        <v>30.74</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8186</v>
+        <v>0.8243</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.47</v>
+        <v>25.49</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5961</v>
+        <v>0.5985</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>27.22</v>
+        <v>27.21</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6051</v>
+        <v>0.6064000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.29</v>
+        <v>26.28</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6959</v>
+        <v>0.6972</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.15</v>
+        <v>24.14</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6975</v>
+        <v>0.7016</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.71</v>
+        <v>30.67</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7847</v>
+        <v>0.7852</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23.68</v>
+        <v>23.65</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4786</v>
+        <v>0.4804</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29.81</v>
+        <v>29.83</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8107</v>
+        <v>0.8121</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.49</v>
+        <v>32.79</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9507</v>
+        <v>0.9526</v>
       </c>
     </row>
     <row r="81">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.8</v>
+        <v>29.79</v>
       </c>
       <c r="C81" t="n">
         <v>0.8198</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.79</v>
+        <v>35.82</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9388</v>
+        <v>0.9393</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.53</v>
+        <v>28.55</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7175</v>
+        <v>0.7193000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.24</v>
+        <v>22.25</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5291</v>
+        <v>0.5323</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21.06</v>
+        <v>21.05</v>
       </c>
       <c r="C85" t="n">
-        <v>0.606</v>
+        <v>0.6096</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.63</v>
+        <v>25.57</v>
       </c>
       <c r="C86" t="n">
-        <v>0.785</v>
+        <v>0.7887</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24.99</v>
+        <v>25.03</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5997</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.37</v>
+        <v>27.38</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6948</v>
+        <v>0.6961000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.69</v>
+        <v>30.73</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8148</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         <v>27.25</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5603</v>
+        <v>0.5614</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.04</v>
+        <v>25.12</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.6496</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>29.08</v>
+        <v>29.1</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7139</v>
+        <v>0.7161999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.62</v>
+        <v>26.68</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7521</v>
+        <v>0.7566000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.85</v>
+        <v>30.9</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8782</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="95">
@@ -1664,7 +1664,7 @@
         <v>26.01</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7157</v>
+        <v>0.7181</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.28</v>
+        <v>26.45</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8054</v>
+        <v>0.8117</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21.94</v>
+        <v>21.91</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3178</v>
+        <v>0.3203</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1703,7 @@
         <v>27.03</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5614</v>
+        <v>0.5629</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.32</v>
+        <v>26.31</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7785</v>
+        <v>0.7806</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.92</v>
+        <v>26.95</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7343</v>
+        <v>0.7379</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.1</v>
+        <v>25.11</v>
       </c>
       <c r="C101" t="n">
-        <v>0.727</v>
+        <v>0.7309</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.55</v>
+        <v>27.59</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7358</v>
+        <v>0.7382</v>
       </c>
     </row>
   </sheetData>
